--- a/artfynd/A 50580-2022 artfynd.xlsx
+++ b/artfynd/A 50580-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50580-2022 artfynd.xlsx
+++ b/artfynd/A 50580-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>104504964</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471121.8342688615</v>
+        <v>471121</v>
       </c>
       <c r="R2" t="n">
-        <v>6531748.040610407</v>
+        <v>6531748</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-11-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +773,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104505377</v>
+        <v>104505742</v>
       </c>
       <c r="B3" t="n">
-        <v>90661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -829,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471245</v>
+        <v>471418</v>
       </c>
       <c r="R3" t="n">
-        <v>6531377</v>
+        <v>6531149</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104505034</v>
+        <v>104505813</v>
       </c>
       <c r="B4" t="n">
-        <v>90065</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -907,26 +882,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -936,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471201</v>
+        <v>471439</v>
       </c>
       <c r="R4" t="n">
-        <v>6531666</v>
+        <v>6531138</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,6 +970,304 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104505034</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471200</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6531666</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104505812</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471446</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6531148</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104505377</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Laxå, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471245</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6531377</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Laxå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Finnerödja</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-11-06</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50580-2022 artfynd.xlsx
+++ b/artfynd/A 50580-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104504964</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505742</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505813</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505034</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505812</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,8 +1298,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104505377</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>